--- a/src/beastmistress/assets/maps/debug.xlsx
+++ b/src/beastmistress/assets/maps/debug.xlsx
@@ -4,23 +4,63 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="120" windowWidth="22020" windowHeight="9024"/>
+    <workbookView xWindow="384" yWindow="120" windowWidth="22020" windowHeight="9024" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="tiles" sheetId="1" r:id="rId1"/>
     <sheet name="objects" sheetId="5" r:id="rId2"/>
+    <sheet name="data" sheetId="6" r:id="rId3"/>
   </sheets>
   <calcPr calcId="145621" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1800" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="15">
   <si>
     <t>NONE</t>
   </si>
   <si>
-    <t>debug</t>
+    <t>grass</t>
+  </si>
+  <si>
+    <t>defaultPlayerStart</t>
+  </si>
+  <si>
+    <t>15,15</t>
+  </si>
+  <si>
+    <t>otherValue</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>intList</t>
+  </si>
+  <si>
+    <t>grass,debug</t>
+  </si>
+  <si>
+    <t>grass,lavender</t>
+  </si>
+  <si>
+    <t>oaktree1</t>
+  </si>
+  <si>
+    <t>grass,obstruction</t>
+  </si>
+  <si>
+    <t>greendress1</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>general</t>
+  </si>
+  <si>
+    <t>canInteract?</t>
   </si>
 </sst>
 </file>
@@ -44,7 +84,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -67,18 +107,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -380,1382 +461,1382 @@
   <sheetData>
     <row r="1" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -1852,1293 +1933,1298 @@
     </row>
     <row r="17" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="obstruction">
+      <formula>NOT(ISERROR(SEARCH("obstruction",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3911,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>0</v>
@@ -4002,7 +4088,7 @@
       <c r="H10" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="2" t="s">
         <v>0</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -4095,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>0</v>
@@ -5913,4 +5999,59 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/beastmistress/assets/maps/debug.xlsx
+++ b/src/beastmistress/assets/maps/debug.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1810" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="19">
   <si>
     <t>NONE</t>
   </si>
@@ -61,6 +61,18 @@
   </si>
   <si>
     <t>canInteract?</t>
+  </si>
+  <si>
+    <t>talkable?</t>
+  </si>
+  <si>
+    <t>standInFrontOf?</t>
+  </si>
+  <si>
+    <t>active?</t>
+  </si>
+  <si>
+    <t>talkingTriggersACutscene?</t>
   </si>
 </sst>
 </file>
@@ -122,36 +134,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -6003,51 +5997,108 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="15.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="3">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="b">
+      <c r="D3" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="3" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/beastmistress/assets/maps/debug.xlsx
+++ b/src/beastmistress/assets/maps/debug.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1822" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="24">
   <si>
     <t>NONE</t>
   </si>
@@ -73,6 +73,21 @@
   </si>
   <si>
     <t>talkingTriggersACutscene?</t>
+  </si>
+  <si>
+    <t>popupTextMessage</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>Talk to Debug NPC (F)</t>
+  </si>
+  <si>
+    <t>whichCutscene?</t>
+  </si>
+  <si>
+    <t>debugNPC1</t>
   </si>
 </sst>
 </file>
@@ -5997,11 +6012,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="15.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="15.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" style="3"/>
+    <col min="4" max="4" width="16.109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -6102,6 +6120,34 @@
         <v>1</v>
       </c>
     </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/beastmistress/assets/maps/debug.xlsx
+++ b/src/beastmistress/assets/maps/debug.xlsx
@@ -11,7 +11,7 @@
     <sheet name="objects" sheetId="5" r:id="rId2"/>
     <sheet name="data" sheetId="6" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621" refMode="R1C1"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -25,9 +25,6 @@
   </si>
   <si>
     <t>defaultPlayerStart</t>
-  </si>
-  <si>
-    <t>15,15</t>
   </si>
   <si>
     <t>otherValue</t>
@@ -88,6 +85,9 @@
   </si>
   <si>
     <t>debugNPC1</t>
+  </si>
+  <si>
+    <t>8,11</t>
   </si>
 </sst>
 </file>
@@ -470,1382 +470,1382 @@
   <sheetData>
     <row r="1" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>1</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
@@ -1942,1290 +1942,1290 @@
     </row>
     <row r="17" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>0</v>
@@ -4190,7 +4190,7 @@
         <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>0</v>
@@ -6024,27 +6024,27 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="D2" s="3">
         <v>2</v>
@@ -6052,13 +6052,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D3" s="3" t="b">
         <v>1</v>
@@ -6066,13 +6066,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D4" s="3" t="b">
         <v>1</v>
@@ -6080,13 +6080,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D5" s="3" t="b">
         <v>1</v>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D6" s="3" t="b">
         <v>1</v>
@@ -6108,13 +6108,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
       </c>
       <c r="D7" s="3" t="b">
         <v>1</v>
@@ -6122,30 +6122,30 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>20</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
